--- a/ig/main/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
+++ b/ig/main/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="643">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="645">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260730120000</t>
+    <t>20260928120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:00:00+01:00</t>
+    <t>2026-09-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1933,6 +1933,12 @@
   </si>
   <si>
     <t>Offre de relayage au domicile</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>Point d'accès de téléconsultation</t>
   </si>
   <si>
     <t/>
@@ -2203,7 +2209,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B309"/>
+  <dimension ref="A1:B310"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -4671,15 +4677,23 @@
         <v>640</v>
       </c>
       <c r="B308" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B309" t="s" s="2">
         <v>642</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="B310" t="s" s="2">
+        <v>644</v>
       </c>
     </row>
   </sheetData>
